--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_Auto_OV.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_Auto_OV.xlsx
@@ -385,16 +385,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>116.6783701562449</v>
+        <v>103.0750614624107</v>
       </c>
       <c r="C2">
-        <v>146.7387086897139</v>
+        <v>138.2688184128351</v>
       </c>
       <c r="D2">
-        <v>157.5081954592841</v>
+        <v>152.3742184726332</v>
       </c>
       <c r="E2">
-        <v>161.154932212816</v>
+        <v>159.8665396867945</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>138.5596299358169</v>
+        <v>126.2640182300956</v>
       </c>
       <c r="C3">
-        <v>174.1517542304422</v>
+        <v>165.7712299273897</v>
       </c>
       <c r="D3">
-        <v>185.4666971773374</v>
+        <v>179.6735255738918</v>
       </c>
       <c r="E3">
-        <v>191.1487947608963</v>
+        <v>189.6362306019926</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>118.8896089632375</v>
+        <v>103.6852000450503</v>
       </c>
       <c r="C4">
-        <v>158.7791750362647</v>
+        <v>147.2739158076036</v>
       </c>
       <c r="D4">
-        <v>174.1949993529752</v>
+        <v>166.9965348870074</v>
       </c>
       <c r="E4">
-        <v>180.4525293287959</v>
+        <v>177.6583624756364</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -436,16 +436,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>91.39267917363892</v>
+        <v>85.31225224642364</v>
       </c>
       <c r="C5">
-        <v>115.2882279211059</v>
+        <v>111.7458514449342</v>
       </c>
       <c r="D5">
-        <v>121.9989767003405</v>
+        <v>118.8231540907232</v>
       </c>
       <c r="E5">
-        <v>126.6490149087627</v>
+        <v>125.7810091878905</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -453,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>77.04948484521005</v>
+        <v>72.32494621101729</v>
       </c>
       <c r="C6">
-        <v>98.97414891610921</v>
+        <v>95.12883547664207</v>
       </c>
       <c r="D6">
-        <v>107.2179615983742</v>
+        <v>104.2646790343612</v>
       </c>
       <c r="E6">
-        <v>110.2001182718041</v>
+        <v>109.4325165289446</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>8.973375454910869</v>
+        <v>8.17136840740249</v>
       </c>
       <c r="C7">
-        <v>10.96695152661196</v>
+        <v>10.39971838330274</v>
       </c>
       <c r="D7">
-        <v>11.59449371557918</v>
+        <v>11.26026739007808</v>
       </c>
       <c r="E7">
-        <v>11.739270508237</v>
+        <v>11.71047343821588</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -487,16 +487,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>223.3695539481475</v>
+        <v>278.7958496905762</v>
       </c>
       <c r="C8">
-        <v>397.6025228418179</v>
+        <v>439.5037943941975</v>
       </c>
       <c r="D8">
-        <v>504.9176477967732</v>
+        <v>536.9390326890999</v>
       </c>
       <c r="E8">
-        <v>587.6187498042602</v>
+        <v>596.7592047311565</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>108.9738911407499</v>
+        <v>113.4515110559422</v>
       </c>
       <c r="C9">
-        <v>139.9331364093279</v>
+        <v>141.6601949050669</v>
       </c>
       <c r="D9">
-        <v>152.4325372754017</v>
+        <v>150.3845285195329</v>
       </c>
       <c r="E9">
-        <v>157.9966361046197</v>
+        <v>157.9771829584103</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -521,16 +521,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>54.71924098799064</v>
+        <v>50.08967047315593</v>
       </c>
       <c r="C10">
-        <v>65.34791658083867</v>
+        <v>61.64798056020581</v>
       </c>
       <c r="D10">
-        <v>68.62978723665572</v>
+        <v>66.15866534611683</v>
       </c>
       <c r="E10">
-        <v>68.78508018512743</v>
+        <v>67.93644006241776</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>9.963107903345096</v>
+        <v>9.112421138259668</v>
       </c>
       <c r="C11">
-        <v>11.33515688433635</v>
+        <v>10.64113399311686</v>
       </c>
       <c r="D11">
-        <v>11.79755924073039</v>
+        <v>11.35175070833474</v>
       </c>
       <c r="E11">
-        <v>12.76687655114364</v>
+        <v>12.60355219171525</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>22.40599374631704</v>
+        <v>23.18688290950162</v>
       </c>
       <c r="C12">
-        <v>28.92705375030485</v>
+        <v>28.15114757475399</v>
       </c>
       <c r="D12">
-        <v>30.87116680100592</v>
+        <v>29.81888165627671</v>
       </c>
       <c r="E12">
-        <v>30.52483917172784</v>
+        <v>30.16171804819896</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -572,16 +572,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>30.0250637443907</v>
+        <v>27.53081813016415</v>
       </c>
       <c r="C13">
-        <v>35.95524721312628</v>
+        <v>33.80737911995156</v>
       </c>
       <c r="D13">
-        <v>38.36997764554268</v>
+        <v>36.95476163194362</v>
       </c>
       <c r="E13">
-        <v>38.96315819180896</v>
+        <v>38.47677008862668</v>
       </c>
     </row>
   </sheetData>

--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_Auto_OV.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_Auto_OV.xlsx
@@ -385,16 +385,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>103.0750614624107</v>
+        <v>3.945456898082706</v>
       </c>
       <c r="C2">
-        <v>138.2688184128351</v>
+        <v>11.24674599530237</v>
       </c>
       <c r="D2">
-        <v>152.3742184726332</v>
+        <v>24.05908712725788</v>
       </c>
       <c r="E2">
-        <v>159.8665396867945</v>
+        <v>38.42945665547946</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>126.2640182300956</v>
+        <v>42.25979385660344</v>
       </c>
       <c r="C3">
-        <v>165.7712299273897</v>
+        <v>102.4277518250538</v>
       </c>
       <c r="D3">
-        <v>179.6735255738918</v>
+        <v>134.9384845126371</v>
       </c>
       <c r="E3">
-        <v>189.6362306019926</v>
+        <v>158.0301921683271</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>103.6852000450503</v>
+        <v>3.937412659938618</v>
       </c>
       <c r="C4">
-        <v>147.2739158076036</v>
+        <v>10.51956541482883</v>
       </c>
       <c r="D4">
-        <v>166.9965348870074</v>
+        <v>19.02492169598819</v>
       </c>
       <c r="E4">
-        <v>177.6583624756364</v>
+        <v>26.12622977582889</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -436,16 +436,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>85.31225224642364</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>111.7458514449342</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>118.8231540907232</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>125.7810091878905</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -453,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>72.32494621101729</v>
+        <v>24.27690502187993</v>
       </c>
       <c r="C6">
-        <v>95.12883547664207</v>
+        <v>40.57943331521095</v>
       </c>
       <c r="D6">
-        <v>104.2646790343612</v>
+        <v>40.83092325821137</v>
       </c>
       <c r="E6">
-        <v>109.4325165289446</v>
+        <v>35.44997014317924</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>8.17136840740249</v>
+        <v>2.723789469134164</v>
       </c>
       <c r="C7">
-        <v>10.39971838330274</v>
+        <v>6.933145588868495</v>
       </c>
       <c r="D7">
-        <v>11.26026739007808</v>
+        <v>8.25752941939059</v>
       </c>
       <c r="E7">
-        <v>11.71047343821588</v>
+        <v>9.368378750572703</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -487,16 +487,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>278.7958496905762</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>439.5037943941975</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>536.9390326890999</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>596.7592047311565</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>113.4515110559422</v>
+        <v>203.7721315082457</v>
       </c>
       <c r="C9">
-        <v>141.6601949050669</v>
+        <v>405.8188192207955</v>
       </c>
       <c r="D9">
-        <v>150.3845285195329</v>
+        <v>585.4776304498321</v>
       </c>
       <c r="E9">
-        <v>157.9771829584103</v>
+        <v>755.5430489315274</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -521,16 +521,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>50.08967047315593</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>61.64798056020581</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>66.15866534611683</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>67.93644006241776</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>9.112421138259668</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>10.64113399311686</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>11.35175070833474</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>12.60355219171525</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>23.18688290950162</v>
+        <v>284.7824849654173</v>
       </c>
       <c r="C12">
-        <v>28.15114757475399</v>
+        <v>375.8178201229658</v>
       </c>
       <c r="D12">
-        <v>29.81888165627671</v>
+        <v>336.9533627159269</v>
       </c>
       <c r="E12">
-        <v>30.16171804819896</v>
+        <v>262.9483111894268</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -572,16 +572,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>27.53081813016415</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>33.80737911995156</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>36.95476163194362</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>38.47677008862668</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_Auto_OV.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_Auto_OV.xlsx
@@ -385,16 +385,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>3.945456898082706</v>
+        <v>13.33186423705432</v>
       </c>
       <c r="C2">
-        <v>11.24674599530237</v>
+        <v>17.88387112405531</v>
       </c>
       <c r="D2">
-        <v>24.05908712725788</v>
+        <v>19.70828214975376</v>
       </c>
       <c r="E2">
-        <v>38.42945665547946</v>
+        <v>20.67734884571714</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>42.25979385660344</v>
+        <v>80.10436187102809</v>
       </c>
       <c r="C3">
-        <v>102.4277518250538</v>
+        <v>105.1685094142198</v>
       </c>
       <c r="D3">
-        <v>134.9384845126371</v>
+        <v>113.9883975891391</v>
       </c>
       <c r="E3">
-        <v>158.0301921683271</v>
+        <v>120.3089324491257</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>3.937412659938618</v>
+        <v>9.604523793646763</v>
       </c>
       <c r="C4">
-        <v>10.51956541482883</v>
+        <v>13.64221535902012</v>
       </c>
       <c r="D4">
-        <v>19.02492169598819</v>
+        <v>15.4691527053228</v>
       </c>
       <c r="E4">
-        <v>26.12622977582889</v>
+        <v>16.45677462932212</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -453,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>24.27690502187993</v>
+        <v>26.72603091160183</v>
       </c>
       <c r="C6">
-        <v>40.57943331521095</v>
+        <v>35.15268701501135</v>
       </c>
       <c r="D6">
-        <v>40.83092325821137</v>
+        <v>38.52862920534188</v>
       </c>
       <c r="E6">
-        <v>35.44997014317924</v>
+        <v>40.43828544239459</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>2.723789469134164</v>
+        <v>5.17519999135491</v>
       </c>
       <c r="C7">
-        <v>6.933145588868495</v>
+        <v>6.586488309425071</v>
       </c>
       <c r="D7">
-        <v>8.25752941939059</v>
+        <v>7.131502680382781</v>
       </c>
       <c r="E7">
-        <v>9.368378750572703</v>
+        <v>7.416633177536724</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>203.7721315082457</v>
+        <v>378.4006210158847</v>
       </c>
       <c r="C9">
-        <v>405.8188192207955</v>
+        <v>472.4864854279169</v>
       </c>
       <c r="D9">
-        <v>585.4776304498321</v>
+        <v>501.5852010548584</v>
       </c>
       <c r="E9">
-        <v>755.5430489315274</v>
+        <v>526.9093693104365</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>284.7824849654173</v>
+        <v>264.8881243775343</v>
       </c>
       <c r="C12">
-        <v>375.8178201229658</v>
+        <v>321.6001352685504</v>
       </c>
       <c r="D12">
-        <v>336.9533627159269</v>
+        <v>340.652413858098</v>
       </c>
       <c r="E12">
-        <v>262.9483111894268</v>
+        <v>344.5689941582223</v>
       </c>
     </row>
     <row r="13" spans="1:5">
